--- a/inst/extdata/medidor_test/10%_interval/Measurements_10.xlsx
+++ b/inst/extdata/medidor_test/10%_interval/Measurements_10.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:AD3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -539,7 +539,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-29 18:09:26</t>
+          <t>2026-06-30 17:16:27</t>
         </is>
       </c>
       <c r="H2">
@@ -554,6 +554,11 @@
       <c r="K2">
         <v>0</v>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
       <c r="M2">
         <v>6.4</v>
       </c>
@@ -569,43 +574,150 @@
         </is>
       </c>
       <c r="Q2">
-        <v>1168.133722870454</v>
+        <v>1171.55663356342</v>
       </c>
       <c r="R2">
-        <v>153.3285628756418</v>
+        <v>160.705258159153</v>
       </c>
       <c r="S2">
-        <v>203.967606151104</v>
+        <v>220.9153005113045</v>
       </c>
       <c r="T2">
-        <v>250.547815913324</v>
+        <v>263.785101929582</v>
       </c>
       <c r="U2">
-        <v>243.7055621008774</v>
+        <v>265.0846845821162</v>
       </c>
       <c r="V2">
-        <v>238.1846367978519</v>
+        <v>243.7328250359398</v>
       </c>
       <c r="W2">
-        <v>184.8064959365552</v>
+        <v>187.4194493642535</v>
       </c>
       <c r="X2">
-        <v>117.7156652625243</v>
+        <v>123.2068585753245</v>
       </c>
       <c r="Y2">
-        <v>57.48904582588398</v>
+        <v>61.6159070370631</v>
       </c>
       <c r="Z2">
-        <v>68.43934026890952</v>
+        <v>76.31107390149867</v>
       </c>
       <c r="AA2">
-        <v>467.7367031678043</v>
+        <v>467.5823029157542</v>
       </c>
       <c r="AC2">
         <v>0.01173462482434246</v>
       </c>
       <c r="AD2">
-        <v>13.7076109825472</v>
+        <v>13.74777755533639</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MA2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2.7k</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>RW-1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Observer 1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Eubalaena australis</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-06-30 17:20:49</t>
+        </is>
+      </c>
+      <c r="H3">
+        <v>0.5</v>
+      </c>
+      <c r="I3">
+        <v>22.5</v>
+      </c>
+      <c r="J3">
+        <v>23</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="M3">
+        <v>6.4</v>
+      </c>
+      <c r="N3">
+        <v>2688</v>
+      </c>
+      <c r="O3">
+        <v>7.6</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>example_whale.png</t>
+        </is>
+      </c>
+      <c r="Q3">
+        <v>1171.55663356342</v>
+      </c>
+      <c r="R3">
+        <v>160.705258159153</v>
+      </c>
+      <c r="S3">
+        <v>220.9153005113045</v>
+      </c>
+      <c r="T3">
+        <v>263.785101929582</v>
+      </c>
+      <c r="U3">
+        <v>265.0846845821162</v>
+      </c>
+      <c r="V3">
+        <v>243.7328250359398</v>
+      </c>
+      <c r="W3">
+        <v>187.4194493642535</v>
+      </c>
+      <c r="X3">
+        <v>123.2068585753245</v>
+      </c>
+      <c r="Y3">
+        <v>61.6159070370631</v>
+      </c>
+      <c r="Z3">
+        <v>76.31107390149867</v>
+      </c>
+      <c r="AA3">
+        <v>467.5823029157542</v>
+      </c>
+      <c r="AC3">
+        <v>0.01173462482434246</v>
+      </c>
+      <c r="AD3">
+        <v>13.74777755533639</v>
       </c>
     </row>
   </sheetData>
